--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T16:33:35+00:00</t>
+    <t>2025-04-24T12:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2180,17 +2180,17 @@
   <dimension ref="A1:AN281"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.18359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="28.78515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="24.67578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="119.41015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="102.375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2199,26 +2199,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="50.03125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.89453125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="50.08203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="42.9375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$281</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10057" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10057" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T16:46:41+00:00</t>
+    <t>2026-05-06T07:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +440,7 @@
     <t>Bundle.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -481,7 +478,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -505,7 +502,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -548,7 +545,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1039,10 +1036,6 @@
     <t>A list is a curated collection of resources.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}</t>
-  </si>
-  <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
   </si>
   <si>
@@ -1167,10 +1160,6 @@
     <t>Usually, this is used for documents other than those defined by FHIR.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}iti-mhd-repl:a DocumetReference replacements needs to relate to a superseded DocumentReference {relatesTo.empty() or (relatesTo.code='replaces' implies relatesTo.target.exists())}</t>
-  </si>
-  <si>
     <t>Document[classCode="DOC" and moodCode="EVN"]</t>
   </si>
   <si>
@@ -1261,7 +1250,7 @@
     <t>the superseded DocumentReference resources</t>
   </si>
   <si>
-    <t>any updated DocumentReference that are part of the SubmissionSet if a new new DocumentReference replaces this DocumentReference.</t>
+    <t>any updated DocumentReference that are part of the SubmissionSet if a new DocumentReference replaces this DocumentReference.</t>
   </si>
   <si>
     <t>Bundle.entry:UpdateDocumentRefs.id</t>
@@ -1754,10 +1743,6 @@
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -1989,21 +1974,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2343,7 +2313,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2455,7 +2425,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2569,7 +2539,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2681,7 +2651,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2793,7 +2763,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2907,7 +2877,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -3021,7 +2991,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -3135,7 +3105,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>128</v>
       </c>
@@ -3249,7 +3219,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>134</v>
       </c>
@@ -3363,7 +3333,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>140</v>
       </c>
@@ -3477,7 +3447,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
@@ -3591,7 +3561,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -3705,7 +3675,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>162</v>
       </c>
@@ -3819,7 +3789,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>171</v>
       </c>
@@ -3933,7 +3903,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>178</v>
       </c>
@@ -4047,7 +4017,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>187</v>
       </c>
@@ -4161,7 +4131,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -4275,7 +4245,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>199</v>
       </c>
@@ -4389,7 +4359,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>204</v>
       </c>
@@ -4501,7 +4471,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
@@ -4615,7 +4585,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>206</v>
       </c>
@@ -4731,7 +4701,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>212</v>
       </c>
@@ -4843,7 +4813,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>215</v>
       </c>
@@ -4955,7 +4925,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>218</v>
       </c>
@@ -4974,7 +4944,7 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
@@ -5067,7 +5037,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>225</v>
       </c>
@@ -5179,7 +5149,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>226</v>
       </c>
@@ -5293,7 +5263,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>227</v>
       </c>
@@ -5409,7 +5379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>228</v>
       </c>
@@ -5521,7 +5491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>231</v>
       </c>
@@ -5654,7 +5624,7 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -5747,7 +5717,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>239</v>
       </c>
@@ -5859,7 +5829,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>243</v>
       </c>
@@ -5971,7 +5941,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>244</v>
       </c>
@@ -6085,7 +6055,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>245</v>
       </c>
@@ -6201,7 +6171,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>246</v>
       </c>
@@ -6315,7 +6285,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>252</v>
       </c>
@@ -6429,7 +6399,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>257</v>
       </c>
@@ -6541,7 +6511,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>261</v>
       </c>
@@ -6653,7 +6623,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>262</v>
       </c>
@@ -6767,7 +6737,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>263</v>
       </c>
@@ -6883,7 +6853,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>264</v>
       </c>
@@ -6995,7 +6965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>269</v>
       </c>
@@ -7109,7 +7079,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>273</v>
       </c>
@@ -7221,7 +7191,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>276</v>
       </c>
@@ -7333,7 +7303,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>278</v>
       </c>
@@ -7445,7 +7415,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>281</v>
       </c>
@@ -7557,7 +7527,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>284</v>
       </c>
@@ -7669,7 +7639,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>288</v>
       </c>
@@ -7781,7 +7751,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>289</v>
       </c>
@@ -7895,7 +7865,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>290</v>
       </c>
@@ -8011,7 +7981,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>291</v>
       </c>
@@ -8123,7 +8093,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>294</v>
       </c>
@@ -8235,7 +8205,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>297</v>
       </c>
@@ -8349,7 +8319,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>301</v>
       </c>
@@ -8463,7 +8433,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>305</v>
       </c>
@@ -8577,7 +8547,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>309</v>
       </c>
@@ -8691,7 +8661,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>313</v>
       </c>
@@ -8803,7 +8773,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>314</v>
       </c>
@@ -8917,7 +8887,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>315</v>
       </c>
@@ -9033,7 +9003,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>316</v>
       </c>
@@ -9145,7 +9115,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>317</v>
       </c>
@@ -9259,7 +9229,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>318</v>
       </c>
@@ -9356,24 +9326,24 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>239</v>
@@ -9483,9 +9453,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>243</v>
@@ -9595,9 +9565,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>244</v>
@@ -9709,9 +9679,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>245</v>
@@ -9825,9 +9795,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>246</v>
@@ -9939,9 +9909,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>252</v>
@@ -10053,9 +10023,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>257</v>
@@ -10165,9 +10135,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>261</v>
@@ -10277,9 +10247,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>262</v>
@@ -10391,9 +10361,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>263</v>
@@ -10507,9 +10477,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>264</v>
@@ -10553,7 +10523,7 @@
         <v>77</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>77</v>
@@ -10619,9 +10589,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>269</v>
@@ -10733,9 +10703,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>273</v>
@@ -10845,9 +10815,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>276</v>
@@ -10957,9 +10927,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>278</v>
@@ -11069,9 +11039,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>281</v>
@@ -11181,9 +11151,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>284</v>
@@ -11293,9 +11263,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>288</v>
@@ -11405,9 +11375,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>289</v>
@@ -11519,9 +11489,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>290</v>
@@ -11635,9 +11605,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>291</v>
@@ -11747,9 +11717,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>294</v>
@@ -11859,9 +11829,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>297</v>
@@ -11973,9 +11943,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>301</v>
@@ -12087,9 +12057,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>305</v>
@@ -12201,15 +12171,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>77</v>
@@ -12234,10 +12204,10 @@
         <v>200</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12315,9 +12285,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>225</v>
@@ -12427,9 +12397,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>226</v>
@@ -12541,9 +12511,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>227</v>
@@ -12657,9 +12627,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>228</v>
@@ -12769,9 +12739,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>231</v>
@@ -12883,9 +12853,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>235</v>
@@ -12911,16 +12881,16 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12982,24 +12952,24 @@
         <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>239</v>
@@ -13109,9 +13079,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>243</v>
@@ -13221,9 +13191,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>244</v>
@@ -13335,9 +13305,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>245</v>
@@ -13451,9 +13421,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>246</v>
@@ -13565,9 +13535,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>252</v>
@@ -13679,9 +13649,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>257</v>
@@ -13791,9 +13761,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>261</v>
@@ -13903,9 +13873,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>262</v>
@@ -14017,9 +13987,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>263</v>
@@ -14133,9 +14103,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>264</v>
@@ -14179,7 +14149,7 @@
         <v>77</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -14245,9 +14215,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>269</v>
@@ -14359,9 +14329,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>273</v>
@@ -14471,9 +14441,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>276</v>
@@ -14583,9 +14553,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>278</v>
@@ -14695,9 +14665,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>281</v>
@@ -14807,9 +14777,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>284</v>
@@ -14919,9 +14889,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>288</v>
@@ -15031,9 +15001,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>289</v>
@@ -15145,9 +15115,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>290</v>
@@ -15261,9 +15231,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>291</v>
@@ -15373,9 +15343,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>294</v>
@@ -15485,9 +15455,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>297</v>
@@ -15599,9 +15569,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>301</v>
@@ -15713,9 +15683,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>305</v>
@@ -15827,15 +15797,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>77</v>
@@ -15860,10 +15830,10 @@
         <v>200</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15941,9 +15911,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>225</v>
@@ -16053,9 +16023,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>226</v>
@@ -16167,9 +16137,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>227</v>
@@ -16283,9 +16253,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>228</v>
@@ -16395,9 +16365,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>231</v>
@@ -16509,9 +16479,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>235</v>
@@ -16537,16 +16507,16 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16623,9 +16593,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>239</v>
@@ -16735,9 +16705,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>243</v>
@@ -16847,9 +16817,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>244</v>
@@ -16961,9 +16931,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>245</v>
@@ -17077,9 +17047,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>246</v>
@@ -17191,9 +17161,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>252</v>
@@ -17305,9 +17275,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>257</v>
@@ -17417,9 +17387,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>261</v>
@@ -17529,9 +17499,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>262</v>
@@ -17643,9 +17613,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>263</v>
@@ -17759,9 +17729,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>264</v>
@@ -17805,7 +17775,7 @@
         <v>77</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>77</v>
@@ -17871,9 +17841,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>269</v>
@@ -17985,9 +17955,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>273</v>
@@ -18097,9 +18067,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>276</v>
@@ -18209,9 +18179,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>278</v>
@@ -18321,9 +18291,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>281</v>
@@ -18433,9 +18403,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>284</v>
@@ -18545,9 +18515,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>288</v>
@@ -18657,9 +18627,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="146" hidden="true">
+    <row r="146">
       <c r="A146" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>289</v>
@@ -18771,9 +18741,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>290</v>
@@ -18887,9 +18857,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>291</v>
@@ -18999,9 +18969,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>294</v>
@@ -19111,9 +19081,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>297</v>
@@ -19225,9 +19195,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>301</v>
@@ -19339,9 +19309,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>305</v>
@@ -19453,15 +19423,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>77</v>
@@ -19486,10 +19456,10 @@
         <v>200</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -19567,9 +19537,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>225</v>
@@ -19679,9 +19649,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>226</v>
@@ -19793,9 +19763,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>227</v>
@@ -19909,9 +19879,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>228</v>
@@ -20021,9 +19991,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>231</v>
@@ -20135,9 +20105,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>235</v>
@@ -20163,16 +20133,16 @@
         <v>77</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -20240,7 +20210,7 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
@@ -20249,9 +20219,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>239</v>
@@ -20361,9 +20331,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>243</v>
@@ -20473,9 +20443,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>244</v>
@@ -20587,9 +20557,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>245</v>
@@ -20703,9 +20673,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>246</v>
@@ -20817,9 +20787,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>252</v>
@@ -20931,9 +20901,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>257</v>
@@ -21043,9 +21013,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>261</v>
@@ -21155,9 +21125,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>262</v>
@@ -21269,9 +21239,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>263</v>
@@ -21385,9 +21355,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>264</v>
@@ -21497,9 +21467,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>269</v>
@@ -21611,9 +21581,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>273</v>
@@ -21723,9 +21693,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>276</v>
@@ -21835,9 +21805,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>278</v>
@@ -21947,9 +21917,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>281</v>
@@ -22059,9 +22029,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>284</v>
@@ -22171,9 +22141,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>288</v>
@@ -22283,9 +22253,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178" hidden="true">
+    <row r="178">
       <c r="A178" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>289</v>
@@ -22397,9 +22367,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>290</v>
@@ -22513,9 +22483,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>291</v>
@@ -22625,9 +22595,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>294</v>
@@ -22737,9 +22707,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="182" hidden="true">
+    <row r="182">
       <c r="A182" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>297</v>
@@ -22851,9 +22821,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>301</v>
@@ -22965,9 +22935,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="184" hidden="true">
+    <row r="184">
       <c r="A184" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>305</v>
@@ -23079,15 +23049,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="185" hidden="true">
+    <row r="185">
       <c r="A185" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>77</v>
@@ -23112,10 +23082,10 @@
         <v>200</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -23193,9 +23163,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186" hidden="true">
+    <row r="186">
       <c r="A186" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>225</v>
@@ -23305,9 +23275,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>226</v>
@@ -23419,9 +23389,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="188" hidden="true">
+    <row r="188">
       <c r="A188" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>227</v>
@@ -23535,9 +23505,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="189" hidden="true">
+    <row r="189">
       <c r="A189" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>228</v>
@@ -23647,9 +23617,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="190" hidden="true">
+    <row r="190">
       <c r="A190" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>231</v>
@@ -23761,9 +23731,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>235</v>
@@ -23789,7 +23759,7 @@
         <v>77</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L191" t="s" s="2">
         <v>81</v>
@@ -23858,7 +23828,7 @@
         <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>84</v>
@@ -23873,9 +23843,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>239</v>
@@ -23985,9 +23955,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="193" hidden="true">
+    <row r="193">
       <c r="A193" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>243</v>
@@ -24097,9 +24067,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="194" hidden="true">
+    <row r="194">
       <c r="A194" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>244</v>
@@ -24211,9 +24181,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="195" hidden="true">
+    <row r="195">
       <c r="A195" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>245</v>
@@ -24327,9 +24297,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="196" hidden="true">
+    <row r="196">
       <c r="A196" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>246</v>
@@ -24441,9 +24411,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="197" hidden="true">
+    <row r="197">
       <c r="A197" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>252</v>
@@ -24555,9 +24525,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="198" hidden="true">
+    <row r="198">
       <c r="A198" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>257</v>
@@ -24667,9 +24637,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="199" hidden="true">
+    <row r="199">
       <c r="A199" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>261</v>
@@ -24779,9 +24749,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="200" hidden="true">
+    <row r="200">
       <c r="A200" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>262</v>
@@ -24893,9 +24863,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201" hidden="true">
+    <row r="201">
       <c r="A201" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>263</v>
@@ -25009,9 +24979,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="202" hidden="true">
+    <row r="202">
       <c r="A202" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>264</v>
@@ -25055,7 +25025,7 @@
         <v>77</v>
       </c>
       <c r="S202" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T202" t="s" s="2">
         <v>77</v>
@@ -25121,9 +25091,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>269</v>
@@ -25235,9 +25205,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="204" hidden="true">
+    <row r="204">
       <c r="A204" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>273</v>
@@ -25347,9 +25317,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>276</v>
@@ -25459,9 +25429,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="206" hidden="true">
+    <row r="206">
       <c r="A206" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>278</v>
@@ -25571,9 +25541,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="207" hidden="true">
+    <row r="207">
       <c r="A207" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>281</v>
@@ -25683,9 +25653,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208" hidden="true">
+    <row r="208">
       <c r="A208" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>284</v>
@@ -25795,9 +25765,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="209" hidden="true">
+    <row r="209">
       <c r="A209" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>288</v>
@@ -25907,9 +25877,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="210" hidden="true">
+    <row r="210">
       <c r="A210" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>289</v>
@@ -26021,9 +25991,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211" hidden="true">
+    <row r="211">
       <c r="A211" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>290</v>
@@ -26137,9 +26107,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="212" hidden="true">
+    <row r="212">
       <c r="A212" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>291</v>
@@ -26249,9 +26219,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="213" hidden="true">
+    <row r="213">
       <c r="A213" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>294</v>
@@ -26361,9 +26331,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="214" hidden="true">
+    <row r="214">
       <c r="A214" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>297</v>
@@ -26475,9 +26445,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="215" hidden="true">
+    <row r="215">
       <c r="A215" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>301</v>
@@ -26589,9 +26559,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216" hidden="true">
+    <row r="216">
       <c r="A216" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>305</v>
@@ -26703,15 +26673,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="217" hidden="true">
+    <row r="217">
       <c r="A217" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>77</v>
@@ -26736,10 +26706,10 @@
         <v>200</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -26817,9 +26787,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="218" hidden="true">
+    <row r="218">
       <c r="A218" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>225</v>
@@ -26929,9 +26899,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="219" hidden="true">
+    <row r="219">
       <c r="A219" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>226</v>
@@ -27043,9 +27013,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220" hidden="true">
+    <row r="220">
       <c r="A220" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>227</v>
@@ -27159,9 +27129,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221" hidden="true">
+    <row r="221">
       <c r="A221" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>228</v>
@@ -27271,9 +27241,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="222" hidden="true">
+    <row r="222">
       <c r="A222" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>231</v>
@@ -27385,9 +27355,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="223" hidden="true">
+    <row r="223">
       <c r="A223" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>235</v>
@@ -27413,7 +27383,7 @@
         <v>77</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>321</v>
@@ -27482,14 +27452,14 @@
         <v>77</v>
       </c>
       <c r="AJ223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL223" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AK223" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL223" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AM223" t="s" s="2">
         <v>77</v>
       </c>
@@ -27497,9 +27467,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="224" hidden="true">
+    <row r="224">
       <c r="A224" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>239</v>
@@ -27609,9 +27579,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="225" hidden="true">
+    <row r="225">
       <c r="A225" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>243</v>
@@ -27721,9 +27691,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="226" hidden="true">
+    <row r="226">
       <c r="A226" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>244</v>
@@ -27835,9 +27805,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="227" hidden="true">
+    <row r="227">
       <c r="A227" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>245</v>
@@ -27951,9 +27921,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="228" hidden="true">
+    <row r="228">
       <c r="A228" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>246</v>
@@ -28065,9 +28035,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="229" hidden="true">
+    <row r="229">
       <c r="A229" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>252</v>
@@ -28179,9 +28149,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="230" hidden="true">
+    <row r="230">
       <c r="A230" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>257</v>
@@ -28291,9 +28261,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="231" hidden="true">
+    <row r="231">
       <c r="A231" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>261</v>
@@ -28403,9 +28373,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>262</v>
@@ -28517,9 +28487,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="233" hidden="true">
+    <row r="233">
       <c r="A233" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>263</v>
@@ -28633,9 +28603,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="234" hidden="true">
+    <row r="234">
       <c r="A234" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>264</v>
@@ -28698,7 +28668,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>77</v>
@@ -28743,9 +28713,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="235" hidden="true">
+    <row r="235">
       <c r="A235" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>269</v>
@@ -28857,9 +28827,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="236" hidden="true">
+    <row r="236">
       <c r="A236" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>273</v>
@@ -28969,9 +28939,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="237" hidden="true">
+    <row r="237">
       <c r="A237" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>276</v>
@@ -29081,9 +29051,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="238" hidden="true">
+    <row r="238">
       <c r="A238" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>278</v>
@@ -29193,9 +29163,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="239" hidden="true">
+    <row r="239">
       <c r="A239" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>281</v>
@@ -29305,9 +29275,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" hidden="true">
+    <row r="240">
       <c r="A240" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>284</v>
@@ -29417,9 +29387,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="241" hidden="true">
+    <row r="241">
       <c r="A241" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>288</v>
@@ -29529,9 +29499,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="242" hidden="true">
+    <row r="242">
       <c r="A242" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>289</v>
@@ -29643,9 +29613,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="243" hidden="true">
+    <row r="243">
       <c r="A243" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>290</v>
@@ -29759,9 +29729,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="244" hidden="true">
+    <row r="244">
       <c r="A244" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>291</v>
@@ -29871,9 +29841,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="245" hidden="true">
+    <row r="245">
       <c r="A245" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>294</v>
@@ -29983,9 +29953,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="246" hidden="true">
+    <row r="246">
       <c r="A246" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>297</v>
@@ -30097,9 +30067,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="247" hidden="true">
+    <row r="247">
       <c r="A247" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>301</v>
@@ -30211,9 +30181,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="248" hidden="true">
+    <row r="248">
       <c r="A248" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>305</v>
@@ -30325,15 +30295,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="249" hidden="true">
+    <row r="249">
       <c r="A249" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D249" t="s" s="2">
         <v>77</v>
@@ -30358,10 +30328,10 @@
         <v>200</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -30439,9 +30409,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="250" hidden="true">
+    <row r="250">
       <c r="A250" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>225</v>
@@ -30551,9 +30521,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="251" hidden="true">
+    <row r="251">
       <c r="A251" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>226</v>
@@ -30665,9 +30635,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="252" hidden="true">
+    <row r="252">
       <c r="A252" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>227</v>
@@ -30781,9 +30751,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="253" hidden="true">
+    <row r="253">
       <c r="A253" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>228</v>
@@ -30893,9 +30863,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="254" hidden="true">
+    <row r="254">
       <c r="A254" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>231</v>
@@ -31007,16 +30977,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="255" hidden="true">
+    <row r="255">
       <c r="A255" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>235</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
@@ -31035,13 +31005,13 @@
         <v>77</v>
       </c>
       <c r="K255" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="L255" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M255" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="L255" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -31104,24 +31074,24 @@
         <v>77</v>
       </c>
       <c r="AJ255" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK255" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL255" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AM255" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN255" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AK255" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL255" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="256" hidden="true">
-      <c r="A256" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>239</v>
@@ -31231,9 +31201,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="257" hidden="true">
+    <row r="257">
       <c r="A257" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>243</v>
@@ -31343,9 +31313,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="258" hidden="true">
+    <row r="258">
       <c r="A258" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>244</v>
@@ -31457,9 +31427,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="259" hidden="true">
+    <row r="259">
       <c r="A259" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>245</v>
@@ -31573,9 +31543,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="260" hidden="true">
+    <row r="260">
       <c r="A260" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>246</v>
@@ -31687,9 +31657,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="261" hidden="true">
+    <row r="261">
       <c r="A261" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>252</v>
@@ -31801,9 +31771,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="262" hidden="true">
+    <row r="262">
       <c r="A262" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>257</v>
@@ -31913,9 +31883,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="263" hidden="true">
+    <row r="263">
       <c r="A263" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>261</v>
@@ -32025,9 +31995,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="264" hidden="true">
+    <row r="264">
       <c r="A264" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>262</v>
@@ -32139,9 +32109,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="265" hidden="true">
+    <row r="265">
       <c r="A265" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>263</v>
@@ -32255,9 +32225,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="266" hidden="true">
+    <row r="266">
       <c r="A266" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>264</v>
@@ -32320,7 +32290,7 @@
       </c>
       <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>77</v>
@@ -32365,9 +32335,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="267" hidden="true">
+    <row r="267">
       <c r="A267" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>269</v>
@@ -32479,9 +32449,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="268" hidden="true">
+    <row r="268">
       <c r="A268" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>273</v>
@@ -32591,9 +32561,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="269" hidden="true">
+    <row r="269">
       <c r="A269" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>276</v>
@@ -32703,9 +32673,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="270" hidden="true">
+    <row r="270">
       <c r="A270" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>278</v>
@@ -32815,9 +32785,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="271" hidden="true">
+    <row r="271">
       <c r="A271" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>281</v>
@@ -32927,9 +32897,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="272" hidden="true">
+    <row r="272">
       <c r="A272" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>284</v>
@@ -33039,9 +33009,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="273" hidden="true">
+    <row r="273">
       <c r="A273" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>288</v>
@@ -33151,9 +33121,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="274" hidden="true">
+    <row r="274">
       <c r="A274" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>289</v>
@@ -33265,9 +33235,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="275" hidden="true">
+    <row r="275">
       <c r="A275" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>290</v>
@@ -33381,9 +33351,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="276" hidden="true">
+    <row r="276">
       <c r="A276" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>291</v>
@@ -33493,9 +33463,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="277" hidden="true">
+    <row r="277">
       <c r="A277" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>294</v>
@@ -33605,9 +33575,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="278" hidden="true">
+    <row r="278">
       <c r="A278" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>297</v>
@@ -33719,9 +33689,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="279" hidden="true">
+    <row r="279">
       <c r="A279" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>301</v>
@@ -33833,9 +33803,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="280" hidden="true">
+    <row r="280">
       <c r="A280" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>305</v>
@@ -33947,12 +33917,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="281" hidden="true">
+    <row r="281">
       <c r="A281" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -33975,19 +33945,19 @@
         <v>88</v>
       </c>
       <c r="K281" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L281" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M281" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N281" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L281" t="s" s="2">
+      <c r="O281" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M281" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N281" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P281" t="s" s="2">
         <v>77</v>
@@ -34036,7 +34006,7 @@
         <v>77</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>78</v>
@@ -34064,24 +34034,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN281">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI280">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
